--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3417,7 +3417,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>21</v>
@@ -3649,7 +3649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>182</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -901,7 +901,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
 </t>
   </si>
   <si>
@@ -1009,7 +1009,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -1975,7 +1975,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="205.50390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="195.8359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,7 +89,7 @@
   <si>
     <t>Ein Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine "MedicationRequest"-Ressource abgebildet.
 Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline, d.h. innerhalb der Ressource), dokumentiert wird.
-Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer geplanten Abgabe dienen. Es werden R5-Backport-Extensions verwendet.</t>
+Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer "Geplanten Abgabe" dienen. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T17:37:50+00:00</t>
+    <t>2026-06-15T21:20:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -709,7 +709,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
+    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine Geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -858,7 +858,7 @@
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE.</t>
+    <t>Quelle der Information. Bedeutung: false: Verordnung durch den Planeintrag erstellenden GDA | true: Fremdmedikation oder Eigenmedikation des Patienten.</t>
   </si>
   <si>
     <t>MedicationRequest.medication[x]</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}e-med-continuous-medication-effectiveDosePeriod:Eine Dauermedikation (courseOfTherapyType = #continuous) darf kein Enddatum besitzen. {courseOfTherapyType.where(coding.code='continuous' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists().not()}e-med-acute-medication-effectiveDosePeriod:Eine Akutmedikation (courseOfTherapyType = #acute) muss ein Enddatum besitzen. {courseOfTherapyType.where(coding.code='acute' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>81</v>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>90</v>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>90</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$75</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2800" uniqueCount="531">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:34:15+00:00</t>
+    <t>2026-08-31T18:38:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -119,7 +119,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/MedicationRequest</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medicationrequest-base</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}e-med-continuous-medication-effectiveDosePeriod:Eine Dauermedikation (courseOfTherapyType = #continuous) darf kein Enddatum besitzen. {courseOfTherapyType.where(coding.code='continuous' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists().not()}e-med-acute-medication-effectiveDosePeriod:Eine Akutmedikation (courseOfTherapyType = #acute) muss ein Enddatum besitzen. {courseOfTherapyType.where(coding.code='acute' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}allDosagesSameCategory:Alle Dosierungsanweisungen eines MedicationRequest müssen dieselbe Dosierungskategorie aufweisen. {dosageInstruction.extension.where(url = 'https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-extension-dosage-category').value.coding.code.distinct().count() = 1}FirstDosageSequenceNumberExists:Wenn mehrere Dosierungsanweisungen vorhanden sind, muss mindestens eine davon die Sequenznummer 1 haben. {dosageInstruction.count() &lt;= 1 or dosageInstruction.sequence.where($this = 1).exists()}e-med-continuous-medication-effectiveDosePeriod:Eine Dauermedikation (courseOfTherapyType = #continuous) darf kein Enddatum besitzen. {courseOfTherapyType.where(coding.code='continuous' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists().not()}e-med-acute-medication-effectiveDosePeriod:Eine Akutmedikation (courseOfTherapyType = #acute) muss ein Enddatum besitzen. {courseOfTherapyType.where(coding.code='acute' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -1272,7 +1272,7 @@
     <t>MedicationRequest.dosageInstruction</t>
   </si>
   <si>
-    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-dosierung}
+    <t xml:space="preserve">Dosage
 </t>
   </si>
   <si>
@@ -1285,10 +1285,67 @@
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:extension.value}
+</t>
+  </si>
+  <si>
     <t>Request.occurrence[x]</t>
   </si>
   <si>
     <t>see dosageInstruction mapping</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:otherDosage</t>
+  </si>
+  <si>
+    <t>otherDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-other-administration}
+</t>
+  </si>
+  <si>
+    <t>How the medication should be taken</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:timedDosage</t>
+  </si>
+  <si>
+    <t>timedDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-timed-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:frequencyDosage</t>
+  </si>
+  <si>
+    <t>frequencyDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-frequency-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:freitextDosage</t>
+  </si>
+  <si>
+    <t>freitextDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-freetext-administration}
+</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction:standardDosage</t>
+  </si>
+  <si>
+    <t>standardDosage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosage {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-dosage-standard-administration}
+</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest</t>
@@ -1962,7 +2019,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.68359375" customWidth="true" bestFit="true"/>
@@ -7135,7 +7192,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>395</v>
       </c>
@@ -7210,16 +7267,14 @@
         <v>21</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>400</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>21</v>
+        <v>257</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>395</v>
@@ -7237,13 +7292,13 @@
         <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>21</v>
@@ -7252,14 +7307,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C46" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="C46" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="D46" t="s" s="2">
         <v>21</v>
       </c>
@@ -7268,10 +7325,10 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>21</v>
@@ -7280,15 +7337,17 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>21</v>
@@ -7337,13 +7396,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -7352,29 +7411,31 @@
         <v>102</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>406</v>
+        <v>21</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
+      <c r="B47" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C47" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="B47" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>21</v>
       </c>
@@ -7383,10 +7444,10 @@
         <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>21</v>
@@ -7395,15 +7456,17 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>193</v>
+        <v>409</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>194</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>21</v>
@@ -7452,28 +7515,28 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>196</v>
+        <v>395</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>197</v>
+        <v>402</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>21</v>
@@ -7482,16 +7545,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7501,7 +7566,7 @@
         <v>81</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>21</v>
@@ -7510,16 +7575,16 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>412</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>199</v>
+        <v>406</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>200</v>
+        <v>398</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>159</v>
+        <v>399</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7569,7 +7634,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>202</v>
+        <v>395</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7581,16 +7646,16 @@
         <v>21</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>197</v>
+        <v>402</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>21</v>
@@ -7599,16 +7664,18 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="D49" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7618,29 +7685,27 @@
         <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>135</v>
+        <v>415</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>21</v>
       </c>
@@ -7688,7 +7753,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7700,16 +7765,16 @@
         <v>21</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>133</v>
+        <v>402</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>21</v>
@@ -7718,14 +7783,16 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>21</v>
       </c>
@@ -7734,10 +7801,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>21</v>
@@ -7746,16 +7813,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7805,13 +7872,13 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>21</v>
@@ -7820,13 +7887,13 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>21</v>
@@ -7837,10 +7904,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7851,7 +7918,7 @@
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>21</v>
@@ -7863,13 +7930,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>193</v>
+        <v>420</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>194</v>
+        <v>421</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>195</v>
+        <v>422</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7920,7 +7987,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>196</v>
+        <v>419</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7932,16 +7999,16 @@
         <v>21</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>21</v>
+        <v>423</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>197</v>
+        <v>424</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>21</v>
@@ -7952,21 +8019,21 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>21</v>
@@ -7978,17 +8045,15 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>135</v>
+        <v>193</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N52" s="2"/>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>21</v>
@@ -8037,19 +8102,19 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>141</v>
+        <v>21</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>21</v>
@@ -8069,14 +8134,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>411</v>
+        <v>156</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8089,26 +8154,24 @@
         <v>21</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>412</v>
+        <v>199</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>413</v>
+        <v>200</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="O53" t="s" s="2">
-        <v>160</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>21</v>
       </c>
@@ -8156,7 +8219,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>414</v>
+        <v>202</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8177,7 +8240,7 @@
         <v>21</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>133</v>
+        <v>197</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>21</v>
@@ -8188,42 +8251,46 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>424</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>21</v>
       </c>
@@ -8271,19 +8338,19 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>21</v>
@@ -8292,7 +8359,7 @@
         <v>21</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>427</v>
+        <v>133</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>21</v>
@@ -8303,10 +8370,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8329,15 +8396,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -8386,7 +8455,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8407,7 +8476,7 @@
         <v>21</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>21</v>
@@ -8418,10 +8487,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8444,13 +8513,13 @@
         <v>21</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>429</v>
+        <v>193</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>434</v>
+        <v>194</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>435</v>
+        <v>195</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8501,7 +8570,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>433</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8513,7 +8582,7 @@
         <v>21</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>21</v>
@@ -8522,7 +8591,7 @@
         <v>21</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>432</v>
+        <v>197</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>21</v>
@@ -8533,21 +8602,21 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>21</v>
+        <v>156</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>21</v>
@@ -8559,20 +8628,18 @@
         <v>21</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>437</v>
+        <v>135</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>438</v>
+        <v>199</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>439</v>
+        <v>200</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>21</v>
       </c>
@@ -8620,28 +8687,28 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>436</v>
+        <v>202</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>442</v>
+        <v>21</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>443</v>
+        <v>197</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>21</v>
@@ -8652,44 +8719,46 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>445</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>21</v>
       </c>
@@ -8737,42 +8806,42 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>449</v>
+        <v>21</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>450</v>
+        <v>133</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>451</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8795,13 +8864,13 @@
         <v>21</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8852,7 +8921,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8870,24 +8939,24 @@
         <v>21</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>455</v>
+        <v>21</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>457</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8910,17 +8979,15 @@
         <v>21</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>429</v>
+        <v>446</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>21</v>
@@ -8969,7 +9036,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8987,10 +9054,10 @@
         <v>21</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>462</v>
+        <v>21</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>21</v>
@@ -9001,10 +9068,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9027,13 +9094,13 @@
         <v>21</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9084,7 +9151,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9105,10 +9172,10 @@
         <v>21</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>336</v>
+        <v>21</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>21</v>
@@ -9116,10 +9183,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9130,7 +9197,7 @@
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>21</v>
@@ -9142,16 +9209,20 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>403</v>
+        <v>454</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>458</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>21</v>
       </c>
@@ -9199,7 +9270,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9217,10 +9288,10 @@
         <v>21</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>21</v>
@@ -9231,10 +9302,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>474</v>
+        <v>461</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9257,15 +9328,17 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>193</v>
+        <v>462</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>194</v>
+        <v>463</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>465</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -9314,7 +9387,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>196</v>
+        <v>461</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9326,41 +9399,41 @@
         <v>21</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>21</v>
+        <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>21</v>
+        <v>466</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>197</v>
+        <v>467</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>21</v>
+        <v>468</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>21</v>
@@ -9372,17 +9445,15 @@
         <v>21</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>441</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>199</v>
+        <v>470</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>159</v>
-      </c>
+        <v>471</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -9431,78 +9502,76 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>202</v>
+        <v>469</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>21</v>
+        <v>472</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>197</v>
+        <v>473</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>21</v>
+        <v>474</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>411</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>446</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>413</v>
+        <v>477</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>160</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>21</v>
       </c>
@@ -9550,28 +9619,28 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>414</v>
+        <v>475</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>21</v>
+        <v>479</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>133</v>
+        <v>480</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>21</v>
@@ -9582,10 +9651,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9593,7 +9662,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>90</v>
@@ -9608,17 +9677,15 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>481</v>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>21</v>
@@ -9643,13 +9710,13 @@
         <v>21</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>482</v>
+        <v>21</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>483</v>
+        <v>21</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>21</v>
@@ -9667,10 +9734,10 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>90</v>
@@ -9685,16 +9752,16 @@
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>472</v>
+        <v>21</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>21</v>
+        <v>336</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>485</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" hidden="true">
@@ -9713,7 +9780,7 @@
         <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>21</v>
@@ -9725,7 +9792,7 @@
         <v>21</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>183</v>
+        <v>420</v>
       </c>
       <c r="L67" t="s" s="2">
         <v>487</v>
@@ -9758,13 +9825,13 @@
         <v>21</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>489</v>
+        <v>21</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>490</v>
+        <v>21</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>21</v>
@@ -9800,24 +9867,24 @@
         <v>21</v>
       </c>
       <c r="AL67" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="AM67" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="B68" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9831,7 +9898,7 @@
         <v>90</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>21</v>
@@ -9840,13 +9907,13 @@
         <v>21</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>495</v>
+        <v>193</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>496</v>
+        <v>194</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>497</v>
+        <v>195</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9897,7 +9964,7 @@
         <v>21</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>494</v>
+        <v>196</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -9909,16 +9976,16 @@
         <v>21</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>21</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>498</v>
+        <v>21</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>491</v>
+        <v>21</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>499</v>
+        <v>197</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>21</v>
@@ -9929,21 +9996,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>501</v>
+        <v>156</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>21</v>
@@ -9955,16 +10022,16 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>502</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>503</v>
+        <v>199</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>504</v>
+        <v>200</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>505</v>
+        <v>159</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10014,7 +10081,7 @@
         <v>21</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>500</v>
+        <v>202</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10026,7 +10093,7 @@
         <v>21</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10035,7 +10102,7 @@
         <v>21</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>506</v>
+        <v>197</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>21</v>
@@ -10046,44 +10113,46 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>21</v>
+        <v>428</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>508</v>
+        <v>135</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>509</v>
+        <v>429</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>510</v>
+        <v>430</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>21</v>
       </c>
@@ -10131,7 +10200,7 @@
         <v>21</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>507</v>
+        <v>431</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10143,26 +10212,607 @@
         <v>21</v>
       </c>
       <c r="AJ70" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="AK70" t="s" s="2">
+      <c r="AK71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K73" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="L73" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="AN70" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO70" t="s" s="2">
+      <c r="M73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO70">
+  <autoFilter ref="A1:AO75">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10172,7 +10822,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI74">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T18:38:38+00:00</t>
+    <t>2026-09-03T18:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medicationrequest-planeintrag.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T18:40:45+00:00</t>
+    <t>2026-09-10T13:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,9 +87,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Ein Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine "MedicationRequest"-Ressource abgebildet.
-Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline, d.h. innerhalb der Ressource), dokumentiert wird.
-Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer "Geplanten Abgabe" dienen. Es werden R5-Backport-Extensions verwendet.</t>
+    <t>Ein Planeintrag im Medikationsplan wird durch eine "MedicationRequest"-Ressource abgebildet.
+Sie enthält genau ein Arzneimittel mit dessen Dosierung, wobei das Arzneimittel verpflichtend mit einer contained Medication-Ressource dokumentiert wird.
+Der Planeintrag kann in weiterer Folge als Grundlage für die Erstellung einer "Geplanten Abgabe" dienen. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -271,7 +271,7 @@
 </t>
   </si>
   <si>
-    <t>Medikationsplaneintrag</t>
+    <t>Planeintrag</t>
   </si>
   <si>
     <t>An order or request for both supply of the medication and the instructions for administration of the medication to a patient. The resource is called "MedicationRequest" rather than "MedicationPrescription" or "MedicationOrder" to generalize the use across inpatient and outpatient settings, including care plans, etc., and to harmonize with workflow patterns.</t>
@@ -471,10 +471,10 @@
 </t>
   </si>
   <si>
-    <t>Zeitraum, in dem die Medikation eingenommen werden soll.</t>
-  </si>
-  <si>
-    <t>Zeitraum, über den die Medikation eingenommen werden soll. Wenn mehrere dosageInstruction-Zeilen vorhanden sind (z. B. bei einer ausschleichenden Dosierung), entspricht dieser Zeitraum dem frühesten Startdatum und dem spätesten Enddatum der dosageInstructions.</t>
+    <t>Zeitraum, in dem das Arzneimittel eingenommen werden soll.</t>
+  </si>
+  <si>
+    <t>R5: `MedicationRequest.effectiveDosePeriod` (new:Period)</t>
   </si>
   <si>
     <t>Element `MedicationRequest.effectiveDosePeriod` has a context of MedicationRequest based on following the parent source element upwards and mapping to `MedicationRequest`.
@@ -535,7 +535,7 @@
 </t>
   </si>
   <si>
-    <t>Medikationsplaneintrag-ID.</t>
+    <t>Planeintrag-ID.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -562,7 +562,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status des Medikationsplaneintrags. Mögliche Ausprägungen: [active | on-hold | completed | stopped | entered-in-error]. Bedeutung: active: Planeintrag einer aktiven Medikation, die eingenommen werden soll | on-hold: Planeintrag ist pausiert, die Therapie ist unterbrochen (Wiederaufnahme vorgesehen) | completed: Therapie gemäß Planeintrag wie geplant durchgeführt und abgeschlossen | stopped: Therapie gemäß Planeintrag vorzeitig gestoppt und abgeschlossen | entered-in-error: Fehlerhafter Planeintrag storniert und abgeschlossen.</t>
+    <t>Status des Planeintrags. Mögliche Ausprägungen: [active | on-hold | completed | stopped | entered-in-error]. Bedeutung: active: Planeintrag einer aktiven Medikation, die eingenommen werden soll | on-hold: Planeintrag ist pausiert, die Therapie ist unterbrochen (Wiederaufnahme vorgesehen) | completed: Therapie gemäß Planeintrag wie geplant durchgeführt und abgeschlossen | stopped: Therapie gemäß Planeintrag vorzeitig gestoppt und abgeschlossen | entered-in-error: Fehlerhafter Planeintrag storniert und abgeschlossen.</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -574,7 +574,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplaneintragStatusVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/PlaneintragStatusVS</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -661,7 +661,7 @@
 </t>
   </si>
   <si>
-    <t>Codierter Grund für den aktuellen Status des Medikationsplaneintrags, z.B. warum ein Medikament abgesetzt wurde. Keine codierte Angabe im Medikationsplaneintrag.</t>
+    <t>Keine codierte Begründung für den Status des Planeintrags.</t>
   </si>
   <si>
     <t>A reference to a code defined by a terminology system.</t>
@@ -685,7 +685,7 @@
     <t>MedicationRequest.statusReason.text</t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status des Medikationsplaneintrags (Freitext), z.B. warum ein Medikament abgesetzt wurde.</t>
+    <t>Begründung für den Status des Planeintrags (Freitext), z.B. warum ein Medikament abgesetzt wurde.</t>
   </si>
   <si>
     <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
@@ -709,7 +709,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine Geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
+    <t>Ein Planeintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine Geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -743,7 +743,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Kategorie zur Unterscheidung eines Medikationsplaneintrags von einer geplanten Abgabe (beide haben intent order)</t>
+    <t>Kategorie zur Unterscheidung eines Planeintrags von einer geplanten Abgabe (beide haben intent order)</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -756,7 +756,7 @@
   &lt;coding&gt;
     &lt;system value="https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS"/&gt;
     &lt;code value="1"/&gt;
-    &lt;display value="Medikationsplaneintrag"/&gt;
+    &lt;display value="Planeintrag"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -780,7 +780,7 @@
     <t>MedicationRequest.priority</t>
   </si>
   <si>
-    <t>Priorität des Medikationsplaneintrag: (req) routine | urgent | asap | stat. Keine Verwendung in Medikationsplaneintrag.</t>
+    <t xml:space="preserve"> Medikationsplaneinträge können nicht mit einer Priorität versehen werden: (req) routine | urgent | asap | stat.</t>
   </si>
   <si>
     <t>Indicates how quickly the Medication Request should be addressed with respect to other requests.</t>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation (und somit die Erstellung einer geplanten Abgabe) untersagt (z.B. bei Allergie).</t>
+    <t>Arzneimittel, die (z.B. aufgrund einer Allergie) nicht eingenommen bzw. verordnet werden dürfen, werden nicht dokumentiert.</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -849,7 +849,7 @@
 </t>
   </si>
   <si>
-    <t>Im Falle einer Fremdmedikation Angabe einer Referenz auf: (Patient | Practitioner | PractitionerRole | RelatedPerson | Organization). Keine Verwendung im Medikationsplan.</t>
+    <t>Keine Verwendung im Medikationsplan.</t>
   </si>
   <si>
     <t>MedicationRequest.reported[x]:reportedBoolean</t>
@@ -905,7 +905,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den der Medikationsplaneintrag ausgestellt werden soll, der über den Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
+    <t>Patient, für den der Planeintrag ausgestellt werden soll, der über den Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -938,7 +938,7 @@
 </t>
   </si>
   <si>
-    <t>Aufenthalt/Begegnung, während dessen der Medikationsplaneintrag erstellt wurde. Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Es wird kein Behandlungskontext dokumentiert.</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -966,7 +966,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zusätzliche Informationen (Ressource Any) (z. B. Größe und Gewicht des Patienten), die die Verschreibung des Medikaments unterstützen. Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Keine Referenzen auf zusätzliche Patienteninformationen (Ressource Any) im Planeintrag.</t>
   </si>
   <si>
     <t>Include additional information (for example, patient height and weight) that supports the ordering of the medication.</t>
@@ -985,7 +985,7 @@
 </t>
   </si>
   <si>
-    <t>Datum der Erstellung des Medikationsplaneintrags.</t>
+    <t>Datum der Erstellung des Planeintrags.</t>
   </si>
   <si>
     <t>The date (and perhaps time) when the prescription was initially written or authored on.</t>
@@ -1013,7 +1013,7 @@
 </t>
   </si>
   <si>
-    <t>Arzt oder Ärztin, die den Medikationsplaneintrag erstellt hat und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
+    <t>Arzt oder Ärztin, die den Planeintrag erstellt hat und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -1078,7 +1078,7 @@
 </t>
   </si>
   <si>
-    <t>Die Person, die den Medikationsplaneintrag im Auftrag eines GDA eingegeben hat.</t>
+    <t>Die Person, die den Planeintrag im Auftrag eines GDA eingegeben hat.</t>
   </si>
   <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
@@ -1152,7 +1152,7 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf eine Richtlinie/Guideline verweist, die von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+    <t>URL, die auf eine Richtlinie/Guideline verweist, die von diesem Planeintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1167,7 +1167,7 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf eine extern gepflegte Richtlinie/Guideline verweist, die von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+    <t>URL, die auf eine extern gepflegte Richtlinie/Guideline verweist, die von diesem Planeintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -1180,7 +1180,7 @@
 </t>
   </si>
   <si>
-    <t>Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -1254,7 +1254,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zum Medikationsplaneintrag.</t>
+    <t>Zusätzliche Informationen zum Planeintrag.</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -1355,7 +1355,7 @@
 </t>
   </si>
   <si>
-    <t>Details zur geplanten Abgabe des Arzneimittels im Medikationsplan. Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Details zur geplanten Abgabe des Arzneimittels im Medikationsplan. Keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>Indicates the specific details for the dispense or medication supply part of a medication request (also known as a Medication Prescription or Medication Order).  Note that this information is not always sent with the order.  There may be in some settings (e.g. hospitals) institutional or system support for completing the dispense details in the pharmacy department.</t>
@@ -1560,7 +1560,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der den Medikationsplaneintrag erstellt). Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der den Planeintrag erstellt). Derzeit keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -1640,7 +1640,7 @@
 </t>
   </si>
   <si>
-    <t>Im Falle einer Änderung wird auf den ersetzten Medikationsplaneintrag verwiesen.</t>
+    <t>Im Falle einer Änderung wird auf den ersetzten Planeintrag verwiesen.</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>
@@ -1663,7 +1663,7 @@
 </t>
   </si>
   <si>
-    <t>Klinisches Problem mit Maßnahme (Referenz auf Ressouce DetectedIssue). Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Klinisches Problem mit Maßnahme (Referenz auf Ressouce DetectedIssue). Keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. Drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -1682,7 +1682,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. Keine Verwendung im Planeintrag.</t>
   </si>
   <si>
     <t>Links to Provenance records for past versions of this resource or fulfilling request or event resources that identify key state transitions or updates that are likely to be relevant to a user looking at the current version of the resource.</t>
@@ -3474,7 +3474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
@@ -3487,13 +3487,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>21</v>
